--- a/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
+++ b/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
+++ b/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
+++ b/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
+++ b/output/StructureDefinition-t-cabs-procedure-beatmung.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-procedure-beatmung</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-procedure-beatmung</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -742,7 +742,7 @@
     <t>beatmungsform</t>
   </si>
   <si>
-    <t>http://t-cabs.org/ValueSet/t-cabs-valueset-Beatmungsform</t>
+    <t>https://bih-cei.github.io/T-CABS/ValueSet/t-cabs-valueset-Beatmungsform</t>
   </si>
   <si>
     <t>Procedure.category.coding:beatmungsform.id</t>
@@ -960,7 +960,7 @@
     <t>beatmungsmodus</t>
   </si>
   <si>
-    <t>http://t-cabs.org/ValueSet/t-cabs-valueset-Beatmungsmodus</t>
+    <t>https://bih-cei.github.io/T-CABS/ValueSet/t-cabs-valueset-Beatmungsmodus</t>
   </si>
   <si>
     <t>Procedure.code.coding:beatmungsmodus.id</t>
@@ -1015,7 +1015,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -1324,7 +1324,7 @@
     <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
-    <t>http://t-cabs.org/ValueSet/t-cabs-valueset-beatmungsstelle</t>
+    <t>https://bih-cei.github.io/T-CABS/ValueSet/t-cabs-valueset-beatmungsstelle</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1508,7 +1508,7 @@
     <t>Procedure.usedReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-device-mds-beatmungsgeraet)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-device-mds-beatmungsgeraet)
 </t>
   </si>
   <si>
@@ -1888,7 +1888,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="61.22265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="54.3984375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.67578125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
